--- a/rules/CORE-001034/positive/01/data/unit-test-coreid-CG0562-positive 1.xlsx
+++ b/rules/CORE-001034/positive/01/data/unit-test-coreid-CG0562-positive 1.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdisc.sharepoint.com/sites/CORERules/Shared Documents/unitTesting/SDTMIG/CG0562/positive/01/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-001034\positive\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="14_{9901569F-2F98-4EF3-86CA-CA652AD07745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F3C785F-D1AD-4FB2-AFF6-FC179B08B973}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{000C1E12-6D91-4537-BFD9-BC585F1A06BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21240" windowHeight="15270" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Datasets" sheetId="2" r:id="rId1"/>
-    <sheet name="Library" sheetId="16" r:id="rId2"/>
+    <sheet name="Library" sheetId="16" r:id="rId1"/>
+    <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="eg.xpt" sheetId="15" r:id="rId3"/>
     <sheet name="vs.xpt" sheetId="17" r:id="rId4"/>
     <sheet name="sv.xpt" sheetId="18" r:id="rId5"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="208">
   <si>
     <t>Filename</t>
   </si>
@@ -613,6 +613,57 @@
   </si>
   <si>
     <t>2022-01-20T13:02</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>43</t>
   </si>
 </sst>
 </file>
@@ -661,7 +712,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -671,12 +722,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -737,13 +782,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1290,6 +1335,32 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6281BC4-1BAD-4CA8-BFF7-3AF8BD159A81}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1335,32 +1406,6 @@
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6281BC4-1BAD-4CA8-BFF7-3AF8BD159A81}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1697,7 +1742,7 @@
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
-      <c r="N5" s="5" t="s">
+      <c r="N5" s="6" t="s">
         <v>55</v>
       </c>
       <c r="O5" s="2" t="s">
@@ -1758,7 +1803,7 @@
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
-      <c r="N6" s="5" t="s">
+      <c r="N6" s="6" t="s">
         <v>60</v>
       </c>
       <c r="O6" s="2" t="s">
@@ -1819,7 +1864,7 @@
       </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
-      <c r="N7" s="5" t="s">
+      <c r="N7" s="6" t="s">
         <v>62</v>
       </c>
       <c r="O7" s="2" t="s">
@@ -1880,8 +1925,8 @@
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
-      <c r="N8" s="5" t="s">
-        <v>55</v>
+      <c r="N8" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>60</v>
@@ -1941,8 +1986,8 @@
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
-      <c r="N9" s="5" t="s">
-        <v>60</v>
+      <c r="N9" s="6" t="s">
+        <v>66</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>60</v>
@@ -2002,8 +2047,8 @@
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
-      <c r="N10" s="5" t="s">
-        <v>62</v>
+      <c r="N10" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>60</v>
@@ -2041,1878 +2086,1893 @@
   <dimension ref="A1:U33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="21" width="20.7109375" style="6" customWidth="1"/>
+    <col min="1" max="21" width="20.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="Q1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="R1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="S1" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="T1" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="U1" s="5" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="O2" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="Q2" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="R2" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="S2" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="T2" s="6" t="s">
+      <c r="T2" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="U2" s="6" t="s">
+      <c r="U2" s="5" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="A3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="K3" s="6" t="s">
+      <c r="E3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="L3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="P3" s="6" t="s">
+      <c r="L3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="P3" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="Q3" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="R3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="S3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="T3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="U3" s="6" t="s">
+      <c r="R3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="U3" s="5" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>8</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>8</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>6</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>24</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>8</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>8</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="5">
         <v>9</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="5">
         <v>200</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <v>8</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="5">
         <v>9</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="5">
         <v>8</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="5">
         <v>11</v>
       </c>
-      <c r="O4" s="6">
+      <c r="O4" s="5">
         <v>1</v>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="5">
         <v>8</v>
       </c>
-      <c r="Q4" s="6">
+      <c r="Q4" s="5">
         <v>8</v>
       </c>
-      <c r="R4" s="6">
+      <c r="R4" s="5">
         <v>200</v>
       </c>
-      <c r="S4" s="6">
+      <c r="S4" s="5">
         <v>9</v>
       </c>
-      <c r="T4" s="6">
+      <c r="T4" s="5">
         <v>10</v>
       </c>
-      <c r="U4" s="6">
+      <c r="U4" s="5">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="6" t="s">
+      <c r="A5" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>1</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="5">
         <v>71</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="Q5" s="6">
+      <c r="P5" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q5" s="5">
         <v>1</v>
       </c>
-      <c r="R5" s="6" t="s">
+      <c r="R5" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="S5" s="6" t="s">
+      <c r="S5" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="T5" s="6" t="s">
+      <c r="T5" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="U5" s="6">
+      <c r="U5" s="5">
         <v>-7</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="6" t="s">
+      <c r="A6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>2</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="5">
         <v>71</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="L6" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="Q6" s="6">
+      <c r="P6" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q6" s="5">
         <v>2</v>
       </c>
-      <c r="R6" s="6" t="s">
+      <c r="R6" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="S6" s="6" t="s">
+      <c r="S6" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="T6" s="6" t="s">
+      <c r="T6" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="U6" s="6">
+      <c r="U6" s="5">
         <v>-2</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="6" t="s">
+      <c r="A7" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>3</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="5">
         <v>83</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L7" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="O7" s="6" t="s">
+      <c r="O7" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="Q7" s="6">
+      <c r="P7" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q7" s="5">
         <v>3</v>
       </c>
-      <c r="R7" s="6" t="s">
+      <c r="R7" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="S7" s="6" t="s">
+      <c r="S7" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="T7" s="6" t="s">
+      <c r="T7" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="U7" s="6">
+      <c r="U7" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="6" t="s">
+      <c r="A8" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>4</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="5">
         <v>79</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="L8" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="Q8" s="6">
+      <c r="P8" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q8" s="5">
         <v>4</v>
       </c>
-      <c r="R8" s="6" t="s">
+      <c r="R8" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="S8" s="6" t="s">
+      <c r="S8" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="T8" s="6" t="s">
+      <c r="T8" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="U8" s="6">
+      <c r="U8" s="5">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" s="6" t="s">
+      <c r="A9" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>5</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="5">
         <v>68</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="L9" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="Q9" s="6">
+      <c r="P9" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q9" s="5">
         <v>5</v>
       </c>
-      <c r="R9" s="6" t="s">
+      <c r="R9" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="S9" s="6" t="s">
+      <c r="S9" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="T9" s="6" t="s">
+      <c r="T9" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="U9" s="6">
+      <c r="U9" s="5">
         <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" s="6" t="s">
+      <c r="A10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>6</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="5">
         <v>77</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="L10" s="5" t="s">
         <v>105</v>
       </c>
       <c r="P10" s="7">
         <v>1</v>
       </c>
-      <c r="Q10" s="6">
+      <c r="Q10" s="5">
         <v>7</v>
       </c>
-      <c r="R10" s="6" t="s">
+      <c r="R10" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="S10" s="6" t="s">
+      <c r="S10" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="T10" s="6" t="s">
+      <c r="T10" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="U10" s="6">
+      <c r="U10" s="5">
         <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="6" t="s">
+      <c r="A11" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>7</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="J11" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="5">
         <v>71</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="L11" s="5" t="s">
         <v>105</v>
       </c>
       <c r="P11" s="7">
         <v>2</v>
       </c>
-      <c r="Q11" s="6">
+      <c r="Q11" s="5">
         <v>7</v>
       </c>
-      <c r="R11" s="6" t="s">
+      <c r="R11" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="S11" s="6" t="s">
+      <c r="S11" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="T11" s="6" t="s">
+      <c r="T11" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="U11" s="6">
+      <c r="U11" s="5">
         <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" s="6" t="s">
+      <c r="A12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <v>8</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="J12" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="5">
         <v>69</v>
       </c>
-      <c r="L12" s="6" t="s">
+      <c r="L12" s="5" t="s">
         <v>105</v>
       </c>
       <c r="P12" s="7">
         <v>3</v>
       </c>
-      <c r="Q12" s="6">
+      <c r="Q12" s="5">
         <v>7</v>
       </c>
-      <c r="R12" s="6" t="s">
+      <c r="R12" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="S12" s="6" t="s">
+      <c r="S12" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="T12" s="6" t="s">
+      <c r="T12" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="U12" s="6">
+      <c r="U12" s="5">
         <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B13" s="6" t="s">
+      <c r="A13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <v>9</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="J13" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="5">
         <v>76</v>
       </c>
-      <c r="L13" s="6" t="s">
+      <c r="L13" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="P13" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="6">
+      <c r="P13" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q13" s="5">
         <v>8</v>
       </c>
-      <c r="R13" s="6" t="s">
+      <c r="R13" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="S13" s="6" t="s">
+      <c r="S13" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="T13" s="6" t="s">
+      <c r="T13" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="U13" s="6">
+      <c r="U13" s="5">
         <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" s="6" t="s">
+      <c r="A14" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="5">
         <v>10</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="I14" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J14" s="6" t="s">
+      <c r="J14" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="K14" s="6">
-        <v>52</v>
-      </c>
-      <c r="L14" s="6" t="s">
+      <c r="K14" s="5">
+        <v>52</v>
+      </c>
+      <c r="L14" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="P14" s="7">
-        <v>2</v>
-      </c>
-      <c r="Q14" s="6">
+      <c r="P14" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q14" s="5">
         <v>8</v>
       </c>
-      <c r="R14" s="6" t="s">
+      <c r="R14" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="S14" s="6" t="s">
+      <c r="S14" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="T14" s="6" t="s">
+      <c r="T14" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="U14" s="6">
+      <c r="U14" s="5">
         <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" s="6" t="s">
+      <c r="A15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="5">
         <v>11</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="H15" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="I15" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J15" s="6" t="s">
+      <c r="J15" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="5">
         <v>60</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="L15" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="P15" s="7">
-        <v>3</v>
-      </c>
-      <c r="Q15" s="6">
+      <c r="P15" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q15" s="5">
         <v>8</v>
       </c>
-      <c r="R15" s="6" t="s">
+      <c r="R15" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="S15" s="6" t="s">
+      <c r="S15" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="T15" s="6" t="s">
+      <c r="T15" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="U15" s="6">
+      <c r="U15" s="5">
         <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" s="6" t="s">
+      <c r="A16" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="5">
         <v>12</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H16" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="I16" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J16" s="6" t="s">
+      <c r="J16" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="5">
         <v>68</v>
       </c>
-      <c r="L16" s="6" t="s">
+      <c r="L16" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="P16" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="6">
+      <c r="P16" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q16" s="5">
         <v>201</v>
       </c>
-      <c r="R16" s="6" t="s">
+      <c r="R16" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="S16" s="6" t="s">
+      <c r="S16" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="T16" s="6" t="s">
+      <c r="T16" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="U16" s="6">
+      <c r="U16" s="5">
         <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" s="6" t="s">
+      <c r="A17" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="5">
         <v>13</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="H17" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="I17" s="6" t="s">
+      <c r="I17" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J17" s="6" t="s">
+      <c r="J17" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="K17" s="6">
+      <c r="K17" s="5">
         <v>72</v>
       </c>
-      <c r="L17" s="6" t="s">
+      <c r="L17" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="P17" s="7">
-        <v>2</v>
-      </c>
-      <c r="Q17" s="6">
+      <c r="P17" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="R17" s="6" t="s">
+      <c r="Q17" s="5">
+        <v>201</v>
+      </c>
+      <c r="R17" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="S17" s="6" t="s">
+      <c r="S17" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="T17" s="6" t="s">
+      <c r="T17" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="U17" s="6">
+      <c r="U17" s="5">
         <v>172</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="6" t="s">
+      <c r="A18" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="5">
         <v>14</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="H18" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="I18" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J18" s="6" t="s">
+      <c r="J18" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K18" s="5">
         <v>68</v>
       </c>
-      <c r="L18" s="6" t="s">
+      <c r="L18" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="P18" s="7">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="6">
+      <c r="P18" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q18" s="5">
         <v>201</v>
       </c>
-      <c r="R18" s="6" t="s">
+      <c r="R18" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="S18" s="6" t="s">
+      <c r="S18" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="T18" s="6" t="s">
+      <c r="T18" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="U18" s="6">
+      <c r="U18" s="5">
         <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="6" t="s">
+      <c r="A19" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="5">
         <v>21</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="H19" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="I19" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="J19" s="6" t="s">
+      <c r="J19" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="K19" s="6">
-        <v>52</v>
-      </c>
-      <c r="L19" s="6" t="s">
+      <c r="K19" s="5">
+        <v>52</v>
+      </c>
+      <c r="L19" s="5" t="s">
         <v>137</v>
       </c>
       <c r="P19" s="7">
         <v>1</v>
       </c>
-      <c r="Q19" s="6">
+      <c r="Q19" s="5">
         <v>7</v>
       </c>
-      <c r="R19" s="6" t="s">
+      <c r="R19" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="S19" s="6" t="s">
+      <c r="S19" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="T19" s="6" t="s">
+      <c r="T19" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="U19" s="6">
+      <c r="U19" s="5">
         <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="6" t="s">
+      <c r="A20" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="5">
         <v>22</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="H20" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="I20" s="6" t="s">
+      <c r="I20" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="J20" s="6" t="s">
+      <c r="J20" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="K20" s="6">
+      <c r="K20" s="5">
         <v>62</v>
       </c>
-      <c r="L20" s="6" t="s">
+      <c r="L20" s="5" t="s">
         <v>137</v>
       </c>
       <c r="P20" s="7">
         <v>2</v>
       </c>
-      <c r="Q20" s="6">
+      <c r="Q20" s="5">
         <v>7</v>
       </c>
-      <c r="R20" s="6" t="s">
+      <c r="R20" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="S20" s="6" t="s">
+      <c r="S20" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="T20" s="6" t="s">
+      <c r="T20" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="U20" s="6">
+      <c r="U20" s="5">
         <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" s="6" t="s">
+      <c r="A21" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="5">
         <v>23</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="I21" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="J21" s="6" t="s">
+      <c r="J21" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="K21" s="6">
+      <c r="K21" s="5">
         <v>62</v>
       </c>
-      <c r="L21" s="6" t="s">
+      <c r="L21" s="5" t="s">
         <v>137</v>
       </c>
       <c r="P21" s="7">
         <v>3</v>
       </c>
-      <c r="Q21" s="6">
+      <c r="Q21" s="5">
         <v>7</v>
       </c>
-      <c r="R21" s="6" t="s">
+      <c r="R21" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="S21" s="6" t="s">
+      <c r="S21" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="T21" s="6" t="s">
+      <c r="T21" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="U21" s="6">
+      <c r="U21" s="5">
         <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="6" t="s">
+      <c r="A22" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="5">
         <v>24</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="H22" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="I22" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="J22" s="6" t="s">
+      <c r="J22" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="K22" s="6">
-        <v>50</v>
-      </c>
-      <c r="L22" s="6" t="s">
+      <c r="K22" s="5">
+        <v>50</v>
+      </c>
+      <c r="L22" s="5" t="s">
         <v>137</v>
       </c>
       <c r="P22" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="Q22" s="6">
+      <c r="Q22" s="5">
         <v>8</v>
       </c>
-      <c r="R22" s="6" t="s">
+      <c r="R22" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="S22" s="6" t="s">
+      <c r="S22" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="T22" s="6" t="s">
+      <c r="T22" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="U22" s="6">
+      <c r="U22" s="5">
         <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" s="6" t="s">
+      <c r="A23" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="5">
         <v>25</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="H23" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="I23" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="J23" s="6" t="s">
+      <c r="J23" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="K23" s="6">
-        <v>52</v>
-      </c>
-      <c r="L23" s="6" t="s">
+      <c r="K23" s="5">
+        <v>52</v>
+      </c>
+      <c r="L23" s="5" t="s">
         <v>137</v>
       </c>
       <c r="P23" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q23" s="6">
+        <v>66</v>
+      </c>
+      <c r="Q23" s="5">
         <v>8</v>
       </c>
-      <c r="R23" s="6" t="s">
+      <c r="R23" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="S23" s="6" t="s">
+      <c r="S23" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="T23" s="6" t="s">
+      <c r="T23" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="U23" s="6">
+      <c r="U23" s="5">
         <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="6" t="s">
+      <c r="A24" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="5">
         <v>26</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="H24" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="I24" s="6" t="s">
+      <c r="I24" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="J24" s="6" t="s">
+      <c r="J24" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="K24" s="6">
+      <c r="K24" s="5">
         <v>54</v>
       </c>
-      <c r="L24" s="6" t="s">
+      <c r="L24" s="5" t="s">
         <v>137</v>
       </c>
       <c r="P24" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q24" s="6">
+        <v>68</v>
+      </c>
+      <c r="Q24" s="5">
         <v>8</v>
       </c>
-      <c r="R24" s="6" t="s">
+      <c r="R24" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="S24" s="6" t="s">
+      <c r="S24" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="T24" s="6" t="s">
+      <c r="T24" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="U24" s="6">
+      <c r="U24" s="5">
         <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" s="6" t="s">
+      <c r="A25" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="5">
         <v>27</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="H25" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="I25" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="J25" s="6" t="s">
+      <c r="J25" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="K25" s="6">
+      <c r="K25" s="5">
         <v>79</v>
       </c>
-      <c r="L25" s="6" t="s">
+      <c r="L25" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="P25" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q25" s="6">
+      <c r="P25" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q25" s="5">
         <v>201</v>
       </c>
-      <c r="R25" s="6" t="s">
+      <c r="R25" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="S25" s="6" t="s">
+      <c r="S25" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="T25" s="6" t="s">
+      <c r="T25" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="U25" s="6">
+      <c r="U25" s="5">
         <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="6" t="s">
+      <c r="A26" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="5">
         <v>28</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="H26" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="I26" s="6" t="s">
+      <c r="I26" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="J26" s="6" t="s">
+      <c r="J26" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="K26" s="6">
+      <c r="K26" s="5">
         <v>98</v>
       </c>
-      <c r="L26" s="6" t="s">
+      <c r="L26" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="P26" s="7">
-        <v>2</v>
-      </c>
-      <c r="Q26" s="6">
+      <c r="P26" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q26" s="5">
         <v>201</v>
       </c>
-      <c r="R26" s="6" t="s">
+      <c r="R26" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="S26" s="6" t="s">
+      <c r="S26" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="T26" s="6" t="s">
+      <c r="T26" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="U26" s="6">
+      <c r="U26" s="5">
         <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="6" t="s">
+      <c r="A27" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="5">
         <v>29</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G27" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="H27" s="6" t="s">
+      <c r="H27" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="I27" s="6" t="s">
+      <c r="I27" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="J27" s="6" t="s">
+      <c r="J27" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="K27" s="6">
+      <c r="K27" s="5">
         <v>94</v>
       </c>
-      <c r="L27" s="6" t="s">
+      <c r="L27" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="P27" s="7">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="6">
+      <c r="P27" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q27" s="5">
         <v>201</v>
       </c>
-      <c r="R27" s="6" t="s">
+      <c r="R27" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="S27" s="6" t="s">
+      <c r="S27" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="T27" s="6" t="s">
+      <c r="T27" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="U27" s="6">
+      <c r="U27" s="5">
         <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" s="6" t="s">
+      <c r="A28" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D28" s="5">
         <v>7</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="H28" s="6" t="s">
+      <c r="H28" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="I28" s="6" t="s">
+      <c r="I28" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J28" s="6" t="s">
+      <c r="J28" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="K28" s="6">
+      <c r="K28" s="5">
         <v>59</v>
       </c>
-      <c r="L28" s="6" t="s">
+      <c r="L28" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="P28" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q28" s="6">
+      <c r="P28" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q28" s="5">
         <v>8</v>
       </c>
-      <c r="R28" s="6" t="s">
+      <c r="R28" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="S28" s="6" t="s">
+      <c r="S28" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="T28" s="6" t="s">
+      <c r="T28" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="U28" s="6">
+      <c r="U28" s="5">
         <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" s="6" t="s">
+      <c r="A29" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="5">
         <v>8</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F29" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="H29" s="6" t="s">
+      <c r="H29" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="I29" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J29" s="6" t="s">
+      <c r="J29" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="K29" s="6">
+      <c r="K29" s="5">
         <v>65</v>
       </c>
-      <c r="L29" s="6" t="s">
+      <c r="L29" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="P29" s="7">
-        <v>2</v>
-      </c>
-      <c r="Q29" s="6">
+      <c r="P29" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q29" s="5">
         <v>8</v>
       </c>
-      <c r="R29" s="6" t="s">
+      <c r="R29" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="S29" s="6" t="s">
+      <c r="S29" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="T29" s="6" t="s">
+      <c r="T29" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="U29" s="6">
+      <c r="U29" s="5">
         <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" s="6" t="s">
+      <c r="A30" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D30" s="5">
         <v>9</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="G30" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="H30" s="6" t="s">
+      <c r="H30" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="I30" s="6" t="s">
+      <c r="I30" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J30" s="6" t="s">
+      <c r="J30" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="K30" s="6">
+      <c r="K30" s="5">
         <v>68</v>
       </c>
-      <c r="L30" s="6" t="s">
+      <c r="L30" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="P30" s="7">
-        <v>3</v>
-      </c>
-      <c r="Q30" s="6">
+      <c r="P30" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q30" s="5">
         <v>8</v>
       </c>
-      <c r="R30" s="6" t="s">
+      <c r="R30" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="S30" s="6" t="s">
+      <c r="S30" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="T30" s="6" t="s">
+      <c r="T30" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="U30" s="6">
+      <c r="U30" s="5">
         <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B31" s="6" t="s">
+      <c r="A31" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="5">
         <v>17</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F31" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="G31" s="6" t="s">
+      <c r="G31" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="H31" s="6" t="s">
+      <c r="H31" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="I31" s="6" t="s">
+      <c r="I31" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="J31" s="6" t="s">
+      <c r="J31" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="K31" s="6">
+      <c r="K31" s="5">
         <v>65</v>
       </c>
-      <c r="L31" s="6" t="s">
+      <c r="L31" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="P31" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q31" s="6">
+      <c r="P31" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q31" s="5">
         <v>8</v>
       </c>
-      <c r="R31" s="6" t="s">
+      <c r="R31" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="S31" s="6" t="s">
+      <c r="S31" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="T31" s="6" t="s">
+      <c r="T31" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="U31" s="6">
+      <c r="U31" s="5">
         <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B32" s="6" t="s">
+      <c r="A32" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D32" s="6">
+      <c r="D32" s="5">
         <v>18</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="G32" s="6" t="s">
+      <c r="G32" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="H32" s="6" t="s">
+      <c r="H32" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="I32" s="6" t="s">
+      <c r="I32" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="J32" s="6" t="s">
+      <c r="J32" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="K32" s="6">
+      <c r="K32" s="5">
         <v>75</v>
       </c>
-      <c r="L32" s="6" t="s">
+      <c r="L32" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="P32" s="7">
-        <v>2</v>
-      </c>
-      <c r="Q32" s="6">
+      <c r="P32" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q32" s="5">
         <v>8</v>
       </c>
-      <c r="R32" s="6" t="s">
+      <c r="R32" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="S32" s="6" t="s">
+      <c r="S32" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="T32" s="6" t="s">
+      <c r="T32" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="U32" s="6">
+      <c r="U32" s="5">
         <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33" s="6" t="s">
+      <c r="A33" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="5">
         <v>19</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="F33" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="G33" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="H33" s="6" t="s">
+      <c r="H33" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="I33" s="6" t="s">
+      <c r="I33" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="J33" s="6" t="s">
+      <c r="J33" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="K33" s="6">
+      <c r="K33" s="5">
         <v>74</v>
       </c>
-      <c r="L33" s="6" t="s">
+      <c r="L33" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="P33" s="7">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="6">
+      <c r="P33" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q33" s="5">
         <v>8</v>
       </c>
-      <c r="R33" s="6" t="s">
+      <c r="R33" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="S33" s="6" t="s">
+      <c r="S33" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="T33" s="6" t="s">
+      <c r="T33" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="U33" s="6">
+      <c r="U33" s="5">
         <v>55</v>
       </c>
     </row>
@@ -3935,659 +3995,659 @@
   <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="10" width="20.7109375" style="6" customWidth="1"/>
+    <col min="1" max="10" width="20.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="5" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="A3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H3" s="6" t="s">
+      <c r="E3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>8</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>8</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>200</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>10</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>10</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>8</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="5">
         <v>8</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="5">
         <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="6" t="s">
+      <c r="A5" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>1</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <v>-7</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="5">
         <v>-7</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="6" t="s">
+      <c r="A6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>2</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <v>-2</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="5">
         <v>-2</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="6" t="s">
+      <c r="A7" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>3</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="5">
         <v>1</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="6" t="s">
+      <c r="A8" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>4</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5">
         <v>14</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="5">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" s="6" t="s">
+      <c r="A9" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>5</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="5">
         <v>27</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="5">
         <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" s="6" t="s">
+      <c r="A10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>5.01</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="5">
         <v>29</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="5">
         <v>29</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="5" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="6" t="s">
+      <c r="A11" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>7</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="5">
         <v>42</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="5">
         <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" s="6" t="s">
+      <c r="A12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <v>8</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="5">
         <v>55</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="5">
         <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B13" s="6" t="s">
+      <c r="A13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <v>101</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="5">
         <v>77</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="5">
         <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" s="6" t="s">
+      <c r="A14" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="5">
         <v>201</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="5">
         <v>172</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="5">
         <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" s="6" t="s">
+      <c r="A15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="5">
         <v>1</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="5">
         <v>-16</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="5">
         <v>-16</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" s="6" t="s">
+      <c r="A16" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="5">
         <v>2</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="5">
         <v>-1</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="5">
         <v>-1</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" s="6" t="s">
+      <c r="A17" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="5">
         <v>3</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H17" s="5">
         <v>1</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I17" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="6" t="s">
+      <c r="A18" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="5">
         <v>4</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H18" s="5">
         <v>14</v>
       </c>
-      <c r="I18" s="6">
+      <c r="I18" s="5">
         <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="6" t="s">
+      <c r="A19" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="5">
         <v>5</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="H19" s="6">
+      <c r="H19" s="5">
         <v>27</v>
       </c>
-      <c r="I19" s="6">
+      <c r="I19" s="5">
         <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="6" t="s">
+      <c r="A20" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="5">
         <v>7</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="H20" s="6">
+      <c r="H20" s="5">
         <v>41</v>
       </c>
-      <c r="I20" s="6">
+      <c r="I20" s="5">
         <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" s="6" t="s">
+      <c r="A21" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="5">
         <v>8</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="H21" s="6">
+      <c r="H21" s="5">
         <v>55</v>
       </c>
-      <c r="I21" s="6">
+      <c r="I21" s="5">
         <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="6" t="s">
+      <c r="A22" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="5">
         <v>9</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="H22" s="6">
+      <c r="H22" s="5">
         <v>61</v>
       </c>
-      <c r="I22" s="6">
+      <c r="I22" s="5">
         <v>61</v>
       </c>
     </row>
@@ -4605,25 +4665,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Comment xmlns="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010090ADB40D834AE945B19FCDA4041AC0CB" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d36826f407302d9fd93d8089214679b0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xmlns:ns3="63ea592b-d684-45c7-8cdc-fad8f8e6bb41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="257daeb82d9c284d9d656fb5e9ad601e" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -4863,7 +4904,46 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Comment xmlns="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E04314CB-2282-4AC1-AC9C-7FC89EF3AFCC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="9dee18c2-6da5-44c1-913e-bf7f393fe0e8"/>
+    <ds:schemaRef ds:uri="63ea592b-d684-45c7-8cdc-fad8f8e6bb41"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CB4DC7C-20D2-408C-91D6-064192CE24D0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -4871,16 +4951,13 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5C4EDDE-D196-4AC8-AD02-E2439740B508}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="9dee18c2-6da5-44c1-913e-bf7f393fe0e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E04314CB-2282-4AC1-AC9C-7FC89EF3AFCC}"/>
 </file>